--- a/rules/CORE-000700/negative/01/data/unit-test-coreid-FB3204-negative.xlsx
+++ b/rules/CORE-000700/negative/01/data/unit-test-coreid-FB3204-negative.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="cm.xpt" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ce.xpt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="lb.xpt" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="fa.xpt" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="se.xpt" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="sv.xpt" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="sm.xpt" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="tv.xpt" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="dm.xpt" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cm.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ce.xpt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lb.xpt" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="fa.xpt" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="se.xpt" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sv.xpt" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sm.xpt" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tv.xpt" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dm.xpt" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2215,7 +2215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2247,6 +2247,452 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Error value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CMDTC</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>CMDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ce.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CEDTC</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ce.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CEDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LBDTC</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>lb.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LBDY</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fa.xpt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FADTC</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fa.xpt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FADY</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>se.xpt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SEDTC</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>se.xpt</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SEDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sv.xpt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SVDTC</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sv.xpt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SVDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sm.xpt</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SMDTC</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>sm.xpt</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SMDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>dm.xpt</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>DMDTC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[ABSENT]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>dm.xpt</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>DMDY</t>
         </is>
       </c>
     </row>
